--- a/quotation_log.xlsx
+++ b/quotation_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,19 +734,139 @@
           <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\images\27042026151353834419.pdf</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-04-27 15:13:54</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>28042026111145925672</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\28042026111145925672.pdf</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-28 11:11:46</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>28042026120212680765</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\28042026120212680765.pdf</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-28 12:02:12</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>28042026122232303390</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\28042026122232303390.pdf</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-28 12:22:32</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>28042026122851697856</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\28042026122851697856.pdf</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-28 12:28:51</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>28042026144500389120</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\28042026144500389120.pdf</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-28 14:45:00</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>28042026145610051832</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\28042026145610051832.pdf</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-28 14:56:10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
         <v>0</v>
       </c>
     </row>

--- a/quotation_log.xlsx
+++ b/quotation_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -854,19 +854,179 @@
           <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\28042026145610051832.pdf</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-04-28 14:56:10</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>28042026172423249268</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\28042026172423249268.pdf</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-28 17:24:23</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>29042026103049202405</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\29042026103049202405.pdf</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-29 10:30:49</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>29042026103049202405</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\29042026103049202405.pdf</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-29 10:30:53</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>29042026120120473603</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\29042026120120473603.pdf</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-29 12:01:20</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>29042026122018560553</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\29042026122018560553.pdf</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-29 12:20:18</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>29042026130202818799</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\29042026130202818799.pdf</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-29 13:02:02</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>29042026130202818799</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\29042026130202818799.pdf</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-29 13:02:05</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>29042026155941411133</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\29042026155941411133.pdf</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-29 15:59:41</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="n">
         <v>0</v>
       </c>
     </row>

--- a/quotation_log.xlsx
+++ b/quotation_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,20 +1014,423 @@
           <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\29042026155941411133.pdf</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>2026-04-29 15:59:41</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>30042026115823235515</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\30042026115823235515.pdf</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-30 11:58:23</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>30042026151331209453</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\30042026151331209453.pdf</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-30 15:13:31</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>30042026151331209453</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\30042026151331209453.pdf</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-30 15:13:34</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>30042026164148893792</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\30042026164148893792.pdf</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Hemil</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1111111111</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-30 16:41:49</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hemil</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>11111</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Hemil</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>04052026120724705608</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\04052026120724705608.pdf</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-04 12:07:25</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>04052026151223055754</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\04052026151223055754.pdf</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DDDD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1111111111</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Arunachal Pradesh</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-04 15:12:23</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>qwerty</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>qwerty</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>05052026093434546249</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\05052026093434546249.pdf</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-05 09:34:34</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>05052026095045418456</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\05052026095045418456.pdf</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>esjrfnejuwe</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-05 09:50:45</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>123412</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>05052026095045418456</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>C:\Users\Shreyas Shah\Desktop\Pipes_Quotation_08042026\quotations\05052026095045418456.pdf</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>esjrfnejuwe</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-05 09:50:48</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>123412</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>05052026130241338211</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://sintexpipesquotation01.blob.core.windows.net/quotation-pdfs/05052026130241338211.pdf</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1111111111</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1111111111</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:02:45</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>qqq</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>1111111111</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>qqq</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>
